--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\budchane\Desktop\New folder\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40C4825-5492-423C-84A8-69E5ECFCA100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{86BC4596-FA5A-49F9-8722-4411CD45C35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{23019ABB-612A-419C-8264-93FB76FED98A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{23019ABB-612A-419C-8264-93FB76FED98A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:D5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
